--- a/foundational_documents/former/DOT_performance_record.xlsx
+++ b/foundational_documents/former/DOT_performance_record.xlsx
@@ -11,10 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Long Rules" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Short Rules" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F1 Sequential Signals" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily P&amp;L" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exit Types" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single Variable Entries" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily P&amp;L" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exit Types" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +66,14 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -98,8 +105,18 @@
         <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8DAEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C5E0B4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -121,11 +138,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -161,6 +222,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -526,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X53"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5078,9 +5148,189 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>Per-signal = STANDALONE (F0: signal_full_records.csv; F1: signal_full_records_F1.csv). Trig column: F0=same-bar triple, F1-seq=sequential latch (gold). Book stats on Portfolio Summary.</t>
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>SV_Hurst_L</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Hurst▲@p97·D2D+</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>6090.6</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>19/20</t>
+        </is>
+      </c>
+      <c r="R53" s="8" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="S53" s="8" t="n">
+        <v>1488.8</v>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v>981.6</v>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v>1779</v>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="W53" s="3" t="n">
+        <v>-118</v>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>SV_FailBrk_L</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>FailBrk▲@p90·D2D-(rev)</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>370</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>19834.1</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>318</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>22/22</t>
+        </is>
+      </c>
+      <c r="R54" s="8" t="n">
+        <v>3794.2</v>
+      </c>
+      <c r="S54" s="8" t="n">
+        <v>4689</v>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v>4711.1</v>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v>3519.7</v>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v>3069.1</v>
+      </c>
+      <c r="W54" s="3" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="X54" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Rows #1-50 = the 50-signal convergence book (per-signal STANDALONE: F0 same-bar triple, F1-seq sequential latch). S1-S2 = the 2 SINGLE-VARIABLE gap entries (S.20): stats shown STANDALONE at LOCK=3 (ungated). In deployment they fire GAP-GATED (only when zero Dots open), contributing 43 (Hurst) + 274 (FailedBreak) trades to the full-system 2,828 — see the Single Variable Entries tab. Book/system totals on Portfolio Summary.</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7915,6 +8165,156 @@
       </c>
       <c r="S38" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>SV_Hurst_L</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Hurst▲@p97·D2D+</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>6090.6</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>19/20</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>-118</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>SV_FailBrk_L</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>FailBrk▲@p90·D2D-(rev)</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>370</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>19834.1</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>318</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>22/22</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9168,7 +9568,326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>THE 2 SINGLE-VARIABLE GAP ENTRIES (S.20) — fire ONLY when zero Dots positions are open; they fill the convergence book’s gaps. SA = standalone (ungated, LOCK=3); Gap = as deployed in the full system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>D2D</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>LOCK</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>SA Trades</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>SA WR% / PF</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>SA Folds / Weeks</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>OOS PF</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>Gap-deployed trades</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Gap WR% / PF</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>Gap net $</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SV_Hurst_L</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Micro_Hurst</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>hi @ p97 (adaptive)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>+1 (aligned)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ADX&gt;=15 &amp; Vol&gt;=300</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>90.7% / 8.96</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>6/6, 19/20</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>85.4% / 5.39</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2,782</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SV_FailBrk_L</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Micro_FailedBreak</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>hi @ p90 (adaptive)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1 (counter/reversion)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ADX&gt;=15 &amp; Vol&gt;=300</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90.0% / 4.82</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6/6, 22/22</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>89.1% / 4.92</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>15,406</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FINDING (the discovery):</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>the F13 single-variable scan found NO lone variable reaching book-level performance (convergence is necessary). These two are the strongest genuine full-span persisters — Micro_Hurst-high (trend persistence: the D2D long is a real trend) and Micro_FailedBreak-extreme (failed break-down -&gt; reversion long). Both LONG-only; the low tails carry no mirror edge.</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="23" t="n"/>
+      <c r="M6" s="23" t="n"/>
+      <c r="N6" s="24" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DEPLOYMENT (the behavior):</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>they fire as NEW entries ONLY when the book is completely flat (zero Dots positions open, live or BE’d), at LOCK=3 (loose lock lets fat-tail winners run), 1.0 lot. Gap-gating removes the redundant overlap trades that stack correlated exposure, so adding them IMPROVES the worst-day vs a crude bolt-in.</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="23" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="24" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PERFORMANCE (in the full system):</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>the 48 + 285 gap trades lift the system from $58,249 (base) to $89,487, worst-day -147.2, OOS PF 6.11. The crude ungated bolt-in was REJECTED (OOS PF 5.42 &lt; flat).</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="23" t="n"/>
+      <c r="N8" s="24" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="B8:N8"/>
+    <mergeCell ref="B7:N7"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9183,7 +9902,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>IN-BOOK PORTFOLIO daily P&amp;L (all 50 together, RUN TM) — true $1/pt, 1 lot</t>
+          <t>DOT FULL SYSTEM daily P&amp;L (pack-engine honest: book + conviction sizing + gap-singles) — true $1/pt, 1-lot base</t>
         </is>
       </c>
     </row>
@@ -9227,23 +9946,23 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026.01.27</t>
+          <t>2026.01.20</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>557</v>
+        <v>3.5</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>557</v>
+        <v>3.5</v>
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
@@ -9254,23 +9973,23 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026.01.28</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>653.8</v>
+        <v>51.3</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>1210.8</v>
+        <v>54.8</v>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
@@ -9281,23 +10000,23 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026.01.29</t>
+          <t>2026.01.27</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>1500.9</v>
+        <v>669.5</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>2711.7</v>
+        <v>724.3</v>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
@@ -9308,23 +10027,23 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.01.28</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>868.9</v>
+        <v>963.1</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>3580.6</v>
+        <v>1687.4</v>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
@@ -9335,23 +10054,23 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026.02.02</t>
+          <t>2026.01.29</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="C7" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="E7" s="16" t="n">
-        <v>31.3</v>
+        <v>2066</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>3611.9</v>
+        <v>3753.4</v>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
@@ -9362,23 +10081,23 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026.02.03</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>51</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>953.3</v>
+        <v>1235</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>4565.2</v>
+        <v>4988.4</v>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
@@ -9389,23 +10108,23 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.02</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>746.4</v>
+        <v>227</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>5311.6</v>
+        <v>5215.4</v>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
@@ -9416,23 +10135,23 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026.02.05</t>
+          <t>2026.02.03</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>1239.3</v>
+        <v>1301.5</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>6550.9</v>
+        <v>6516.9</v>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
@@ -9443,50 +10162,50 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026.02.09</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-63</v>
+        <v>1302.4</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>6487.9</v>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>7819.3</v>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026.02.10</t>
+          <t>2026.02.05</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>16.6</v>
+        <v>1794.9</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>6504.5</v>
+        <v>9614.200000000001</v>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
@@ -9497,23 +10216,23 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026.02.11</t>
+          <t>2026.02.06</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>1021.7</v>
+        <v>270.2</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>7526.2</v>
+        <v>9884.4</v>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
@@ -9524,23 +10243,23 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026.02.12</t>
+          <t>2026.02.09</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>2643.1</v>
+        <v>7.5</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>10169.3</v>
+        <v>9891.9</v>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
@@ -9551,23 +10270,23 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026.02.13</t>
+          <t>2026.02.10</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>386.2</v>
+        <v>116.5</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>10555.5</v>
+        <v>10008.4</v>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
@@ -9578,23 +10297,23 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026.02.16</t>
+          <t>2026.02.11</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>52.2</v>
+        <v>1183.5</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>10607.7</v>
+        <v>11191.9</v>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
@@ -9605,23 +10324,23 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026.02.17</t>
+          <t>2026.02.12</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>1311.4</v>
+        <v>2785.4</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>11919.1</v>
+        <v>13977.3</v>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
@@ -9632,23 +10351,23 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026.02.18</t>
+          <t>2026.02.13</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>451.2</v>
+        <v>855.4</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>12370.3</v>
+        <v>14832.7</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -9659,23 +10378,23 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.02.16</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>196.2</v>
+        <v>71</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>12566.5</v>
+        <v>14903.7</v>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
@@ -9686,23 +10405,23 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026.02.20</t>
+          <t>2026.02.17</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>1215.8</v>
+        <v>1672.1</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>13782.3</v>
+        <v>16575.8</v>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
@@ -9713,23 +10432,23 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026.02.23</t>
+          <t>2026.02.18</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>730.5</v>
+        <v>665.9</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>14512.8</v>
+        <v>17241.7</v>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
@@ -9740,23 +10459,23 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026.02.24</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>646.5</v>
+        <v>430</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>15159.3</v>
+        <v>17671.7</v>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
@@ -9767,23 +10486,23 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026.02.25</t>
+          <t>2026.02.20</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>59</v>
+        <v>1635.1</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>15218.3</v>
+        <v>19306.8</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -9794,23 +10513,23 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026.02.26</t>
+          <t>2026.02.23</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>218.8</v>
+        <v>973.4</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>15437.1</v>
+        <v>20280.2</v>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
@@ -9821,23 +10540,23 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.02.24</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>520.4</v>
+        <v>1527.5</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>15957.5</v>
+        <v>21807.7</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
@@ -9848,23 +10567,23 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026.03.02</t>
+          <t>2026.02.25</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>691.1</v>
+        <v>113.9</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>16648.6</v>
+        <v>21921.6</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
@@ -9875,23 +10594,23 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026.03.03</t>
+          <t>2026.02.26</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>606.2</v>
+        <v>336.2</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>17254.8</v>
+        <v>22257.8</v>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
@@ -9902,23 +10621,23 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026.03.04</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E28" s="16" t="n">
-        <v>88.5</v>
+        <v>854.2</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>17343.3</v>
+        <v>23112</v>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
@@ -9929,23 +10648,23 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026.03.05</t>
+          <t>2026.03.02</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>358.5</v>
+        <v>966.9</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>17701.8</v>
+        <v>24078.9</v>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
@@ -9956,23 +10675,23 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026.03.06</t>
+          <t>2026.03.03</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>2194.3</v>
+        <v>1561.8</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>19896.1</v>
+        <v>25640.7</v>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
@@ -9983,23 +10702,23 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026.03.09</t>
+          <t>2026.03.04</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>1401.9</v>
+        <v>439.7</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>21298</v>
+        <v>26080.4</v>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
@@ -10010,23 +10729,23 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026.03.10</t>
+          <t>2026.03.05</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>537.5</v>
+        <v>912.6</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>21835.5</v>
+        <v>26993</v>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
@@ -10037,23 +10756,23 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026.03.11</t>
+          <t>2026.03.06</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>628.8</v>
+        <v>2614.8</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>22464.3</v>
+        <v>29607.8</v>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
@@ -10064,23 +10783,23 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026.03.12</t>
+          <t>2026.03.09</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>704.1</v>
+        <v>2215.6</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>23168.4</v>
+        <v>31823.4</v>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
@@ -10091,23 +10810,23 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026.03.13</t>
+          <t>2026.03.10</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>46.5</v>
+        <v>886.8</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>23214.9</v>
+        <v>32710.2</v>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
@@ -10118,23 +10837,23 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026.03.16</t>
+          <t>2026.03.11</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E36" s="16" t="n">
-        <v>123.1</v>
+        <v>1434.7</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>23338</v>
+        <v>34144.9</v>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
@@ -10145,23 +10864,23 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026.03.17</t>
+          <t>2026.03.12</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="D37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E37" s="16" t="n">
-        <v>23.4</v>
+        <v>1599.3</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>23361.4</v>
+        <v>35744.2</v>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
@@ -10172,23 +10891,23 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026.03.18</t>
+          <t>2026.03.13</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>765.7</v>
+        <v>389.2</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>24127.1</v>
+        <v>36133.4</v>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
@@ -10199,23 +10918,23 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026.03.19</t>
+          <t>2026.03.16</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>299.1</v>
+        <v>373.4</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>24426.2</v>
+        <v>36506.8</v>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
@@ -10226,50 +10945,50 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026.03.20</t>
+          <t>2026.03.17</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>-67.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>24358.8</v>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>36598.9</v>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026.03.23</t>
+          <t>2026.03.18</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>2777.7</v>
+        <v>1060.7</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>27136.5</v>
+        <v>37659.6</v>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
@@ -10280,23 +10999,23 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026.03.24</t>
+          <t>2026.03.19</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>418.6</v>
+        <v>689.4</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>27555.1</v>
+        <v>38349</v>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
@@ -10307,50 +11026,50 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026.03.25</t>
+          <t>2026.03.20</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>671.9</v>
+        <v>-64.3</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>28227</v>
-      </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>38284.7</v>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026.03.26</t>
+          <t>2026.03.23</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>658.2</v>
+        <v>4089.3</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>28885.2</v>
+        <v>42374</v>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
@@ -10361,23 +11080,23 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026.03.27</t>
+          <t>2026.03.24</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>374.9</v>
+        <v>767.5</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>29260.1</v>
+        <v>43141.5</v>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
@@ -10388,23 +11107,23 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026.03.30</t>
+          <t>2026.03.25</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>365.5</v>
+        <v>1439.1</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>29625.6</v>
+        <v>44580.6</v>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
@@ -10415,23 +11134,23 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026.03.31</t>
+          <t>2026.03.26</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>956.8</v>
+        <v>546.3</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>30582.4</v>
+        <v>45126.9</v>
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
@@ -10442,23 +11161,23 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.03.27</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>20</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>17</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>366.2</v>
+        <v>476.8</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>30948.6</v>
+        <v>45603.7</v>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
@@ -10469,23 +11188,23 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026.04.02</t>
+          <t>2026.03.30</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>1399.1</v>
+        <v>848</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>32347.7</v>
+        <v>46451.7</v>
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
@@ -10496,23 +11215,23 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026.04.06</t>
+          <t>2026.03.31</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>153</v>
+        <v>1709.7</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>32500.7</v>
+        <v>48161.4</v>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
@@ -10523,23 +11242,23 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026.04.07</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>1247.4</v>
+        <v>698.1</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>33748.1</v>
+        <v>48859.5</v>
       </c>
       <c r="G51" s="17" t="inlineStr">
         <is>
@@ -10550,23 +11269,23 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026.04.08</t>
+          <t>2026.04.02</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E52" s="16" t="n">
-        <v>1515.4</v>
+        <v>1645.6</v>
       </c>
       <c r="F52" s="16" t="n">
-        <v>35263.5</v>
+        <v>50505.1</v>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
@@ -10577,23 +11296,23 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026.04.09</t>
+          <t>2026.04.06</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>154.2</v>
+        <v>284.1</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>35417.7</v>
+        <v>50789.2</v>
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
@@ -10604,23 +11323,23 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026.04.10</t>
+          <t>2026.04.07</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E54" s="16" t="n">
-        <v>129.1</v>
+        <v>1793.6</v>
       </c>
       <c r="F54" s="16" t="n">
-        <v>35546.8</v>
+        <v>52582.8</v>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
@@ -10631,23 +11350,23 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026.04.13</t>
+          <t>2026.04.08</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>961</v>
+        <v>2370.6</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>36507.8</v>
+        <v>54953.4</v>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
@@ -10658,23 +11377,23 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.09</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E56" s="16" t="n">
-        <v>51.5</v>
+        <v>199.3</v>
       </c>
       <c r="F56" s="16" t="n">
-        <v>36559.3</v>
+        <v>55152.7</v>
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
@@ -10685,23 +11404,23 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026.04.15</t>
+          <t>2026.04.10</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>106.9</v>
+        <v>169.8</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>36666.2</v>
+        <v>55322.5</v>
       </c>
       <c r="G57" s="17" t="inlineStr">
         <is>
@@ -10712,23 +11431,23 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026.04.16</t>
+          <t>2026.04.13</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E58" s="16" t="n">
-        <v>262.5</v>
+        <v>1041.5</v>
       </c>
       <c r="F58" s="16" t="n">
-        <v>36928.7</v>
+        <v>56364</v>
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
@@ -10739,23 +11458,23 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026.04.17</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>125.5</v>
+        <v>56.7</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>37054.2</v>
+        <v>56420.7</v>
       </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
@@ -10766,23 +11485,23 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026.04.20</t>
+          <t>2026.04.15</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="16" t="n">
-        <v>21.1</v>
+        <v>114.7</v>
       </c>
       <c r="F60" s="16" t="n">
-        <v>37075.3</v>
+        <v>56535.4</v>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
@@ -10793,23 +11512,23 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026.04.21</t>
+          <t>2026.04.16</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>1185.4</v>
+        <v>488</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>38260.7</v>
+        <v>57023.4</v>
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
@@ -10820,23 +11539,23 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.04.17</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E62" s="16" t="n">
-        <v>101.1</v>
+        <v>125.5</v>
       </c>
       <c r="F62" s="16" t="n">
-        <v>38361.8</v>
+        <v>57148.9</v>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
@@ -10847,23 +11566,23 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026.04.23</t>
+          <t>2026.04.20</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>700.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F63" s="16" t="n">
-        <v>39062.2</v>
+        <v>57239.3</v>
       </c>
       <c r="G63" s="17" t="inlineStr">
         <is>
@@ -10874,23 +11593,23 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026.04.24</t>
+          <t>2026.04.21</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E64" s="16" t="n">
-        <v>222.2</v>
+        <v>1700.9</v>
       </c>
       <c r="F64" s="16" t="n">
-        <v>39284.4</v>
+        <v>58940.2</v>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
@@ -10901,23 +11620,23 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026.04.27</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>69.3</v>
+        <v>210.3</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>39353.7</v>
+        <v>59150.5</v>
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
@@ -10928,23 +11647,23 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026.04.28</t>
+          <t>2026.04.23</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" s="16" t="n">
-        <v>29.6</v>
+        <v>968</v>
       </c>
       <c r="F66" s="16" t="n">
-        <v>39383.3</v>
+        <v>60118.5</v>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
@@ -10955,50 +11674,50 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026.04.29</t>
+          <t>2026.04.24</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>-64.90000000000001</v>
+        <v>404.5</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>39318.4</v>
-      </c>
-      <c r="G67" s="18" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>60523</v>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026.04.30</t>
+          <t>2026.04.27</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="16" t="n">
-        <v>188.4</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F68" s="16" t="n">
-        <v>39506.8</v>
+        <v>60610.9</v>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
@@ -11009,23 +11728,23 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026.05.01</t>
+          <t>2026.04.28</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E69" s="16" t="n">
-        <v>173.3</v>
+        <v>35.1</v>
       </c>
       <c r="F69" s="16" t="n">
-        <v>39680.1</v>
+        <v>60646</v>
       </c>
       <c r="G69" s="17" t="inlineStr">
         <is>
@@ -11036,23 +11755,23 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.29</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E70" s="16" t="n">
-        <v>618.7</v>
+        <v>16.4</v>
       </c>
       <c r="F70" s="16" t="n">
-        <v>40298.8</v>
+        <v>60662.4</v>
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
@@ -11063,23 +11782,23 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026.05.05</t>
+          <t>2026.04.30</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E71" s="16" t="n">
-        <v>96.8</v>
+        <v>377.4</v>
       </c>
       <c r="F71" s="16" t="n">
-        <v>40395.6</v>
+        <v>61039.8</v>
       </c>
       <c r="G71" s="17" t="inlineStr">
         <is>
@@ -11090,23 +11809,23 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026.05.06</t>
+          <t>2026.05.01</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>13</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" s="16" t="n">
-        <v>400.1</v>
+        <v>219</v>
       </c>
       <c r="F72" s="16" t="n">
-        <v>40795.7</v>
+        <v>61258.8</v>
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
@@ -11117,23 +11836,23 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026.05.07</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>409.8</v>
+        <v>705.3</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>41205.5</v>
+        <v>61964.1</v>
       </c>
       <c r="G73" s="17" t="inlineStr">
         <is>
@@ -11144,23 +11863,23 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026.05.08</t>
+          <t>2026.05.05</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E74" s="16" t="n">
-        <v>21.6</v>
+        <v>290</v>
       </c>
       <c r="F74" s="16" t="n">
-        <v>41227.1</v>
+        <v>62254.1</v>
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
@@ -11171,50 +11890,50 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026.05.11</t>
+          <t>2026.05.06</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="16" t="n">
-        <v>-36.1</v>
+        <v>379.9</v>
       </c>
       <c r="F75" s="16" t="n">
-        <v>41191</v>
-      </c>
-      <c r="G75" s="18" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>62634</v>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026.05.12</t>
+          <t>2026.05.07</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E76" s="16" t="n">
-        <v>450.3</v>
+        <v>576.8</v>
       </c>
       <c r="F76" s="16" t="n">
-        <v>41641.3</v>
+        <v>63210.8</v>
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
@@ -11225,34 +11944,34 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026.05.13</t>
+          <t>2026.05.08</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E77" s="16" t="n">
-        <v>-127.5</v>
+        <v>117.5</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>41513.8</v>
-      </c>
-      <c r="G77" s="18" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>63328.3</v>
+      </c>
+      <c r="G77" s="17" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026.05.14</t>
+          <t>2026.05.11</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
@@ -11265,10 +11984,10 @@
         <v>2</v>
       </c>
       <c r="E78" s="16" t="n">
-        <v>-38.1</v>
+        <v>-30.4</v>
       </c>
       <c r="F78" s="16" t="n">
-        <v>41475.7</v>
+        <v>63297.9</v>
       </c>
       <c r="G78" s="18" t="inlineStr">
         <is>
@@ -11279,23 +11998,23 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026.05.15</t>
+          <t>2026.05.12</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>365.1</v>
+        <v>450.3</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>41840.8</v>
+        <v>63748.2</v>
       </c>
       <c r="G79" s="17" t="inlineStr">
         <is>
@@ -11306,50 +12025,50 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026.05.18</t>
+          <t>2026.05.13</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E80" s="16" t="n">
-        <v>203.6</v>
+        <v>-153.7</v>
       </c>
       <c r="F80" s="16" t="n">
-        <v>42044.4</v>
-      </c>
-      <c r="G80" s="17" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>63594.5</v>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026.05.19</t>
+          <t>2026.05.14</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>698.5</v>
+        <v>240.5</v>
       </c>
       <c r="F81" s="16" t="n">
-        <v>42742.9</v>
+        <v>63835</v>
       </c>
       <c r="G81" s="17" t="inlineStr">
         <is>
@@ -11360,23 +12079,23 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026.05.20</t>
+          <t>2026.05.15</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" s="16" t="n">
-        <v>2339.6</v>
+        <v>554.1</v>
       </c>
       <c r="F82" s="16" t="n">
-        <v>45082.5</v>
+        <v>64389.1</v>
       </c>
       <c r="G82" s="17" t="inlineStr">
         <is>
@@ -11387,23 +12106,23 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026.05.21</t>
+          <t>2026.05.18</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>1273.2</v>
+        <v>531.7</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>46355.7</v>
+        <v>64920.8</v>
       </c>
       <c r="G83" s="17" t="inlineStr">
         <is>
@@ -11414,23 +12133,23 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026.05.22</t>
+          <t>2026.05.19</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E84" s="16" t="n">
-        <v>65.2</v>
+        <v>853.9</v>
       </c>
       <c r="F84" s="16" t="n">
-        <v>46420.9</v>
+        <v>65774.7</v>
       </c>
       <c r="G84" s="17" t="inlineStr">
         <is>
@@ -11441,23 +12160,23 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026.05.26</t>
+          <t>2026.05.20</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E85" s="16" t="n">
-        <v>151.2</v>
+        <v>5016.9</v>
       </c>
       <c r="F85" s="16" t="n">
-        <v>46572.1</v>
+        <v>70791.60000000001</v>
       </c>
       <c r="G85" s="17" t="inlineStr">
         <is>
@@ -11468,23 +12187,23 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026.05.27</t>
+          <t>2026.05.21</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>36</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>912.2</v>
+        <v>1691.2</v>
       </c>
       <c r="F86" s="16" t="n">
-        <v>47484.3</v>
+        <v>72482.8</v>
       </c>
       <c r="G86" s="17" t="inlineStr">
         <is>
@@ -11495,23 +12214,23 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026.05.28</t>
+          <t>2026.05.22</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>249.5</v>
+        <v>255.6</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>47733.8</v>
+        <v>72738.39999999999</v>
       </c>
       <c r="G87" s="17" t="inlineStr">
         <is>
@@ -11522,23 +12241,23 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026.05.29</t>
+          <t>2026.05.26</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="16" t="n">
-        <v>13.5</v>
+        <v>216.6</v>
       </c>
       <c r="F88" s="16" t="n">
-        <v>47747.3</v>
+        <v>72955</v>
       </c>
       <c r="G88" s="17" t="inlineStr">
         <is>
@@ -11549,23 +12268,23 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026.06.01</t>
+          <t>2026.05.27</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E89" s="16" t="n">
-        <v>311.7</v>
+        <v>1142.2</v>
       </c>
       <c r="F89" s="16" t="n">
-        <v>48059</v>
+        <v>74097.2</v>
       </c>
       <c r="G89" s="17" t="inlineStr">
         <is>
@@ -11576,23 +12295,23 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026.06.02</t>
+          <t>2026.05.28</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D90" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E90" s="16" t="n">
-        <v>61.9</v>
+        <v>344.3</v>
       </c>
       <c r="F90" s="16" t="n">
-        <v>48120.9</v>
+        <v>74441.5</v>
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
@@ -11603,23 +12322,23 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026.06.03</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="16" t="n">
-        <v>198.5</v>
+        <v>50</v>
       </c>
       <c r="F91" s="16" t="n">
-        <v>48319.4</v>
+        <v>74491.5</v>
       </c>
       <c r="G91" s="17" t="inlineStr">
         <is>
@@ -11630,50 +12349,50 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026.06.04</t>
+          <t>2026.06.01</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" s="16" t="n">
-        <v>-70.8</v>
+        <v>441.4</v>
       </c>
       <c r="F92" s="16" t="n">
-        <v>48248.6</v>
-      </c>
-      <c r="G92" s="18" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>74932.89999999999</v>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026.06.05</t>
+          <t>2026.06.02</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>61.1</v>
+        <v>118</v>
       </c>
       <c r="F93" s="16" t="n">
-        <v>48309.7</v>
+        <v>75050.89999999999</v>
       </c>
       <c r="G93" s="17" t="inlineStr">
         <is>
@@ -11684,23 +12403,23 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026.06.08</t>
+          <t>2026.06.03</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="16" t="n">
-        <v>472.4</v>
+        <v>362.2</v>
       </c>
       <c r="F94" s="16" t="n">
-        <v>48782.1</v>
+        <v>75413.10000000001</v>
       </c>
       <c r="G94" s="17" t="inlineStr">
         <is>
@@ -11711,50 +12430,50 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026.06.09</t>
+          <t>2026.06.04</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E95" s="16" t="n">
-        <v>1327.9</v>
+        <v>-88.40000000000001</v>
       </c>
       <c r="F95" s="16" t="n">
-        <v>50110</v>
-      </c>
-      <c r="G95" s="17" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>75324.7</v>
+      </c>
+      <c r="G95" s="18" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026.06.10</t>
+          <t>2026.06.05</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E96" s="16" t="n">
-        <v>902.5</v>
+        <v>302</v>
       </c>
       <c r="F96" s="16" t="n">
-        <v>51012.5</v>
+        <v>75626.7</v>
       </c>
       <c r="G96" s="17" t="inlineStr">
         <is>
@@ -11765,23 +12484,23 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026.06.11</t>
+          <t>2026.06.08</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>1271.3</v>
+        <v>908.2</v>
       </c>
       <c r="F97" s="16" t="n">
-        <v>52283.8</v>
+        <v>76534.89999999999</v>
       </c>
       <c r="G97" s="17" t="inlineStr">
         <is>
@@ -11792,23 +12511,23 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026.06.12</t>
+          <t>2026.06.09</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E98" s="16" t="n">
-        <v>1029.7</v>
+        <v>1903.1</v>
       </c>
       <c r="F98" s="16" t="n">
-        <v>53313.5</v>
+        <v>78438</v>
       </c>
       <c r="G98" s="17" t="inlineStr">
         <is>
@@ -11819,23 +12538,23 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026.06.15</t>
+          <t>2026.06.10</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>56.7</v>
+        <v>1315.1</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>53370.2</v>
+        <v>79753.10000000001</v>
       </c>
       <c r="G99" s="17" t="inlineStr">
         <is>
@@ -11846,23 +12565,23 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026.06.16</t>
+          <t>2026.06.11</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E100" s="16" t="n">
-        <v>77.2</v>
+        <v>1853.4</v>
       </c>
       <c r="F100" s="16" t="n">
-        <v>53447.4</v>
+        <v>81606.5</v>
       </c>
       <c r="G100" s="17" t="inlineStr">
         <is>
@@ -11873,23 +12592,23 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026.06.17</t>
+          <t>2026.06.12</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" s="16" t="n">
-        <v>1119</v>
+        <v>1182</v>
       </c>
       <c r="F101" s="16" t="n">
-        <v>54566.4</v>
+        <v>82788.5</v>
       </c>
       <c r="G101" s="17" t="inlineStr">
         <is>
@@ -11900,23 +12619,23 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026.06.18</t>
+          <t>2026.06.15</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E102" s="16" t="n">
-        <v>88.09999999999999</v>
+        <v>134.6</v>
       </c>
       <c r="F102" s="16" t="n">
-        <v>54654.5</v>
+        <v>82923.10000000001</v>
       </c>
       <c r="G102" s="17" t="inlineStr">
         <is>
@@ -11927,23 +12646,23 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
+          <t>2026.06.16</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E103" s="16" t="n">
-        <v>30.4</v>
+        <v>179.1</v>
       </c>
       <c r="F103" s="16" t="n">
-        <v>54684.9</v>
+        <v>83102.2</v>
       </c>
       <c r="G103" s="17" t="inlineStr">
         <is>
@@ -11954,23 +12673,23 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026.06.22</t>
+          <t>2026.06.17</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E104" s="16" t="n">
-        <v>425.5</v>
+        <v>1301.5</v>
       </c>
       <c r="F104" s="16" t="n">
-        <v>55110.4</v>
+        <v>84403.7</v>
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
@@ -11981,79 +12700,160 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026.06.23</t>
+          <t>2026.06.18</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>330.1</v>
+        <v>-45</v>
       </c>
       <c r="F105" s="16" t="n">
-        <v>55440.5</v>
-      </c>
-      <c r="G105" s="17" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>84358.7</v>
+      </c>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026.06.24</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" s="16" t="n">
-        <v>1110.9</v>
+        <v>-100.9</v>
       </c>
       <c r="F106" s="16" t="n">
-        <v>56551.4</v>
-      </c>
-      <c r="G106" s="17" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>84257.8</v>
+      </c>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
+          <t>2026.06.22</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>643.5</v>
+      </c>
+      <c r="F107" s="16" t="n">
+        <v>84901.3</v>
+      </c>
+      <c r="G107" s="17" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2026.06.23</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>436.4</v>
+      </c>
+      <c r="F108" s="16" t="n">
+        <v>85337.7</v>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2026.06.24</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>1648.1</v>
+      </c>
+      <c r="F109" s="16" t="n">
+        <v>86985.8</v>
+      </c>
+      <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
           <t>2026.06.25</t>
         </is>
       </c>
-      <c r="B107" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>1697.2</v>
-      </c>
-      <c r="F107" s="16" t="n">
-        <v>58248.6</v>
-      </c>
-      <c r="G107" s="17" t="inlineStr">
+      <c r="B110" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>2501.2</v>
+      </c>
+      <c r="F110" s="16" t="n">
+        <v>89487</v>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -12067,7 +12867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12130,20 +12930,20 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.0702496826068557</v>
+        <v>0.07469342251950947</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-67.09999999999999</v>
+        <v>-85</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>-11143</v>
+        <v>-17087</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Initial SL: min(ATR×2,150) base / min(ATR×4,150) on momentum entries. Loss.</t>
+          <t>Initial SL (base ATR×2 / momentum ATR×4, $150 cap). Loss.</t>
         </is>
       </c>
     </row>
@@ -12154,16 +12954,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1810</v>
+        <v>2086</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.7659754549301735</v>
+        <v>0.7751765143069491</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21.1</v>
+        <v>32</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>38219</v>
+        <v>66727.8</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -12178,20 +12978,20 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.1616589081675836</v>
+        <v>0.1445559271646228</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>82.2</v>
+        <v>102.5</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>31404</v>
+        <v>39873.1</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>LeapFrog trail (tier≥3). Runner win.</t>
+          <t>LeapFrog trail / gap-single LOCK=3 runner. Runner win.</t>
         </is>
       </c>
     </row>
@@ -12202,16 +13002,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.00211595429538722</v>
+        <v>0.005202526941657376</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-46.4</v>
+        <v>-12.7</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>-232</v>
+        <v>-178.4</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -12227,13 +13027,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12250,12 +13050,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>RUN (momentum-runner)</t>
+          <t>DOT full system (S.20)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>S.7 base</t>
+          <t>convergence base</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -12267,7 +13067,7 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>IN-BOOK PORTFOLIO — BOOK-50 (v1/FINAL, 50 signals = 48 F0 + 2 F1, 37L/13S)</t>
+          <t>DOT FULL SYSTEM — BOOK-50 (48 F0 + 2 F1) + conviction self-scaling + 2 gap-singles (S.20)</t>
         </is>
       </c>
     </row>
@@ -12277,11 +13077,15 @@
           <t>Total trades</t>
         </is>
       </c>
-      <c r="B3" s="20" t="n">
-        <v>2363</v>
-      </c>
-      <c r="C3" s="19" t="n">
-        <v>2370</v>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>2691</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>2363</t>
+        </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
@@ -12295,11 +13099,15 @@
           <t>Trading days</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n">
-        <v>105</v>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>105</v>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
@@ -12315,7 +13123,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
@@ -12331,15 +13139,19 @@
           <t>Profit Factor</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>5.95</v>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>6.15</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>RUN=validated upgrade; S.7=ratified base</t>
+          <t>full system = pack-engine honest reproduction (modelled $90,103 carried a research-harness artifact); base = engine-validated/frozen</t>
         </is>
       </c>
     </row>
@@ -12351,12 +13163,12 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
+          <t>89,487</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
           <t>58,249</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>56,341</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -12371,11 +13183,15 @@
           <t>Avg $/trade</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>23.8</v>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
       </c>
       <c r="D8" s="19" t="inlineStr"/>
     </row>
@@ -12392,15 +13208,19 @@
           <t>Worst Day $</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
-        <v>-127.5</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>-127.5</v>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>-153.7</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>-127.5</t>
+        </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>19× inside FTMO -$2,500 daily gate</t>
+          <t>16× inside FTMO -$2,500 daily gate</t>
         </is>
       </c>
     </row>
@@ -12410,15 +13230,19 @@
           <t>Max Drawdown $</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
-        <v>-165.6</v>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>-165.6</v>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>-153.7</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>-165.6</t>
+        </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>60× inside FTMO -$10,000 total-DD gate</t>
+          <t>68× inside FTMO -$10,000 total-DD gate</t>
         </is>
       </c>
     </row>
@@ -12450,11 +13274,15 @@
           <t>min-fold PF</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>5.56</v>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
       </c>
       <c r="D14" s="19" t="inlineStr"/>
     </row>
@@ -12466,7 +13294,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>22/22</t>
+          <t>23/23</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
@@ -12488,17 +13316,17 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
           <t>5/5</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>Mon-Fri all net-positive</t>
+          <t>all trading weekdays net-positive</t>
         </is>
       </c>
     </row>
@@ -12510,12 +13338,12 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
           <t>5.69</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>5.56</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -12532,12 +13360,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
+          <t>25,049</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
           <t>14,625</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>14,222</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -12554,10 +13382,14 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
+          <t>2085 / 606 (3.44:1)</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
           <t>1758 / 605 (2.91:1)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr"/>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>climate-appropriate long-lean</t>
@@ -12577,11 +13409,15 @@
           <t>OOS Profit Factor</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="C22" s="19" t="n">
-        <v>6.37</v>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>6.81</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>6.99</t>
+        </is>
       </c>
       <c r="D22" s="19" t="inlineStr"/>
     </row>
@@ -12593,12 +13429,12 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
+          <t>92.5%</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
           <t>93.1%</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>93.2%</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr"/>
@@ -12609,11 +13445,15 @@
           <t>OOS Worst Day $</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
-        <v>-127.5</v>
-      </c>
-      <c r="C24" s="19" t="n">
-        <v>-127.5</v>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>-153.7</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>-127.5</t>
+        </is>
       </c>
       <c r="D24" s="19" t="inlineStr"/>
     </row>
@@ -12625,12 +13465,12 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
+          <t>28,447</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
           <t>18,742</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>16,783</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr"/>
@@ -12638,7 +13478,7 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>EXIT MIX (RUN) &amp; TRIGGER MIX</t>
+          <t>EXIT MIX (full system) &amp; TRIGGER MIX</t>
         </is>
       </c>
     </row>
@@ -12650,10 +13490,14 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
+          <t>2086 / 389</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
           <t>1810 / 382</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr"/>
       <c r="D28" s="19" t="inlineStr">
         <is>
           <t>small wins / runners</t>
@@ -12668,10 +13512,14 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
+          <t>201 / 14</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
           <t>166 / 5</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr"/>
       <c r="D29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
@@ -12682,28 +13530,202 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>48 F0 (same-bar) + 2 F1 (sequential)</t>
+          <t>48 F0 + 2 F1 book | +conviction sizing (Hurst 2x / recentFB 1.25x) | +2 gap-singles</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr"/>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>8/8 structure coverage</t>
+          <t>8/8 structures + conviction/gap layer; DEPLOY 1-LOT BASE ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>S.20 OPTION MAP (all pack-engine, 1-lot base)</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A — flat book (no conviction)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>$58,277</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B — Hurst-x2 sizing only</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>$66,434</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>worst-day held -127.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>G' — Hurst-x2 + gap-singles (recentFB off)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>$84,554</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>worst-day -127.5 (tail-lighter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>G — all-on (ADOPTED)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>$89,487</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>worst-day -153.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>E — crude bolt-in</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>dropped OOS below flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>S.20 TRADE POPULATION (honest, G all-on)</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>book x1.0</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1,339</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hurst x2.0</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>recentFB x1.25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>gap-Hurst (single)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>gap-FailedBreak (single)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>NOTE: the earlier modelled $90,103 / 2,828 tr / x2=254 carried a research-harness jar-sharing artifact (book double-counted); pack engine reproduces the honest $89,487 — 0.7% correction, no conclusion changes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12856,7 +13878,7 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>diamond-35 → +5 F0 co-firers (40) → +18 F0 structure fillers (58) → leave-one-out trim to 48 → +2 F1 structure-fills → BOOK-50 → 6-lot live-risk jar → per-bar execution model → momentum-conditional initial SL.</t>
+          <t>diamond-35 → +5 F0 co-firers (40) → +18 F0 structure fillers (58) → leave-one-out trim to 48 → +2 F1 structure-fills → BOOK-50 → 6-lot live-risk jar → per-bar execution model → momentum-conditional initial SL → conviction self-scaling + gap-singles (S.20).</t>
         </is>
       </c>
     </row>

--- a/foundational_documents/former/DOT_performance_record.xlsx
+++ b/foundational_documents/former/DOT_performance_record.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exit Types" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Summary" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D2D" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,7 +74,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +114,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C5E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -186,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -231,6 +237,8 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5339,6 +5347,394 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>D2D — THE FOUNDING SYSTEM (adaptive break-of-structure / directional-flip engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Anthony's original custom-OBVf-driven directional system, live in equiDOT.cs; ratified TM (native SuperTrend trail FORBIDDEN). The 9th market structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>STANDALONE THRONE SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr"/>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>32 (18L / 14S)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>both directions</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>96.9%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>one loss in ~5 months (a single -$153 SL, in March)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16.89</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net P&amp;L $</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2,431</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1-lot base, true $1/pt (STANDALONE — separate from the $92,347 combined system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Worst Day $</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-153.0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>inside the FTMO -$2,500 daily gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Max Drawdown $</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-153.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Folds positive / min-fold PF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6/6 / 1.72</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>March holds the lone loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OOS (May-Jun)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>n12, 100% WR, PF 999, net $1,111</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>no OOS losers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Exit mix</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SL 1 (-153) / BE 25 (850) / LF 6 (1,734)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>the runner (LF) carries the net</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Per-fold PF</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jan 999 / Feb 999 / Mar 1.72 / Apr 999 / May 999 / Jun 999</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>LONG / SHORT RULES (separate standalone configs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>WR% / PF</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Net $ / Worst Day / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D2D LONG-only</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>100.0% / 999</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>$1,651 / +20 / NO losing day (max-DD 0.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D2D SHORT-only</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>92.9% / 6.10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>$780 / -153 / the lone system loss is here (March)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>ROLES IN THE COMBINED SYSTEM (S.21 crown jewel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C1 D2D-Conviction</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2x sizer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>D2D_Signal==dir &amp; ADX&gt;=30 &amp; Micro_Hurst&gt;=p30 -&gt; up-size a book trade 2x (higher-mult-wins, never 4x); the ONLY short conviction source</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G1 D2D-Gap-Filler</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>flat-2-lot</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>throne entry fired when zero Dots open -&gt; flat 2.0 lots, bypasses conviction (no 4x); 14 trades (4L/10S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>Crown-jewel contribution: Role 2 conviction +$1,015 + Role 1 gap +$1,900 -&gt; combined DOT+D2D system $92,347 (verified DIRECTLY, not summed). This tab records the STANDALONE object; $92,347 is the combined-system canonical.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -13033,7 +13429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -13546,9 +13942,6 @@
           <t>S.20 OPTION MAP (all pack-engine, 1-lot base)</t>
         </is>
       </c>
-      <c r="B32" s="28" t="n"/>
-      <c r="C32" s="28" t="n"/>
-      <c r="D32" s="28" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13641,9 +14034,6 @@
           <t>S.20 TRADE POPULATION (honest, G all-on)</t>
         </is>
       </c>
-      <c r="B39" s="28" t="n"/>
-      <c r="C39" s="28" t="n"/>
-      <c r="D39" s="28" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13712,14 +14102,215 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>S.21 D2D CROWN JEWEL — COMPONENT MAP (RATIFIED, Auditor PASS 2026-07-17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DOT-alone (S.20, warm-up-guarded)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>$89,432</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>daily worst-day -153.7 (baseline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>+ Role 2 — D2D-conviction (both dir)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>+$1,015</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2x book trades; ONLY short conviction source</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>+ Role 1 — D2D-gap (flat 2-lot, 14 tr)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>+$1,900</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>fires when zero Dots open; offsets worst day</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <f> CROWN JEWEL (all roles)</f>
+        <v/>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>$92,347</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>daily worst-day -104.4 (IMPROVES from -153.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>S.21 RATIFIED STATS (built gap-path engine, true $1/pt, 1-lot base)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2,698</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Daily Worst Day $</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>-104.4</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>24.7x inside FTMO -$2,500 daily gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Daily Max Drawdown $</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>-145.9</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>inside FTMO -$10,000 total-DD gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Folds positive / min-fold PF</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>6/6 / 5.39</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>min PF well above the 4.0 floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OOS PF / OOS net $</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>6.96 / 29,326</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>fixed system measured May-Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>ROLES INTERACT via the shared 6-lot jar + short conviction — the combined $92,347 is verified DIRECTLY, not summed from the component deltas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>NOTE: the modelled $92,567 is SUPERSEDED by the built $92,347 (~$220 admission-timing displacement, immaterial). Build-guards Auditor-proven: short_mult sizes shorts (book x2 210-&gt;249 with Role 2); D2D-gap all 2.0 lots, no 4x. Oracle/wf/core byte-identical.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
